--- a/outputs/CTN_SharePoint_DB設計_20260725.xlsx
+++ b/outputs/CTN_SharePoint_DB設計_20260725.xlsx
@@ -20,16 +20,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_要確認事項" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_リスト一覧'!$A$4:$K$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_列定義'!$A$5:$K$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_リスト一覧'!$A$4:$K$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_列定義'!$A$5:$K$134</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_Payload構造'!$A$5:$J$178</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_リレーション'!$A$4:$H$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_選択肢マスタ'!$A$5:$E$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_ロジック実装マップ'!$A$5:$K$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_画面データ連携'!$A$5:$H$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_制限対策'!$A$5:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_選択肢マスタ'!$A$5:$E$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_ロジック実装マップ'!$A$5:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_画面データ連携'!$A$5:$H$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_制限対策'!$A$5:$D$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09_権限・監査'!$A$14:$D$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10_要確認事項'!$A$5:$H$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10_要確認事項'!$A$5:$H$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -574,338 +574,442 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>版 / 作成日</t>
+          <t>版 / 更新日</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1.0 / 2026-07-25</t>
+          <t>1.1 / 2026-07-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>対象システム</t>
+          <t>改訂履歴</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>治験届（CTN: Clinical Trial Notification）管理システム</t>
+          <t>1.0 (2026-07-25) 初版。1.1 (2026-07-26) 提出パッケージ出力（届書PDF＋CTN XML）の main マージを受けて §5「PDF/XML 出力の位置づけ」を追加し、CtnPdfGeneratedAt 列・CtnGeneratedOutputs ライブラリ・ロジック2件・画面連携1件を追記。既存の列定義・Payload構造は変更なし。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>生成元</t>
+          <t>対象システム</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>demo/app/src/ctn/ctn-schema.json（14テーブル/207列）＋ types.ts（UIドメインモデル）</t>
+          <t>治験届（CTN: Clinical Trial Notification）管理システム</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>根拠文書</t>
+          <t>生成元</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ctn-spfx/docs/spfx-methodology.md（方式B 設計判断）／ctn-spfx/docs/ctn-spfx-migration-brief.md §4（データ設計）／CLAUDE.md（採番ツリー原則）</t>
+          <t>demo/app/src/ctn/ctn-schema.json（14テーブル/207列）＋ types.ts（UIドメインモデル）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>根拠文書</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ctn-spfx/docs/spfx-methodology.md（方式B 設計判断）／ctn-spfx/docs/ctn-spfx-migration-brief.md §4（データ設計）／CLAUDE.md（採番ツリー原則）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
           <t>再生成コマンド</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>python tools/gen-sharepoint-db-design.py</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>1. 前提アーキテクチャ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>実行基盤</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>SharePoint ページ / Teams タブ上の SPFx Web パーツ「CtnSuite」。M365 ライセンスのみで稼働（Power Apps Premium 不要）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>認証</t>
+          <t>実行基盤</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SharePoint のユーザーコンテキスト（pageContext）。アプリ側の実装ゼロ。操作ユーザー（actor）は loginName を正とし自己申告にしない</t>
+          <t>SharePoint ページ / Teams タブ上の SPFx Web パーツ「CtnSuite」。M365 ライセンスのみで稼働（Power Apps Premium 不要）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>データアクセス</t>
+          <t>認証</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>React コンポーネント → CtnRepository（抽象） → SharePointCtnRepository（spHttpClient / SP REST）。コンポーネントからの直接 REST 呼び出しは禁止</t>
+          <t>SharePoint のユーザーコンテキスト（pageContext）。アプリ側の実装ゼロ。操作ユーザー（actor）は loginName を正とし自己申告にしない</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>データアクセス</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>React コンポーネント → CtnRepository（抽象） → SharePointCtnRepository（spHttpClient / SP REST）。コンポーネントからの直接 REST 呼び出しは禁止</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>ドメインロジック</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>logic.ts / derive.ts / xml.ts / rules.ts の純粋関数を変更せず流用。保存・承認・提出でリポジトリ層が必ず再実行する</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2. 中核となる設計判断</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>(1) 届は「集約JSON＋昇格列」で1リストに保存する</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Dataverse 構想の14テーブル正規化を SharePoint に持ち込まない。理由は3点。① ドメインモデル Notification が既に集約であり、updateNotification(n) は集約全体の置換を契約とする。② SharePoint にはリスト横断トランザクションが無い。子を6リストに割ると1回の保存が非原子的になり、採番・XML生成の前提が壊れる。集約JSONなら常に「1アイテム1書き込み＝原子的」。③ リストのバージョン管理がそのまま「届のスナップショット履歴」として機能する。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>(2) 昇格列は投影であって正本ではない</t>
+          <t>(1) 届は「集約JSON＋昇格列」で1リストに保存する</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CtnPayload（集約JSON）が正本。昇格列は一覧表示・フィルタ・ダッシュボード集計のための投影。保存時に Payload と昇格列を必ず同一の書き込みで更新する（別々に更新しない）。</t>
+          <t>Dataverse 構想の14テーブル正規化を SharePoint に持ち込まない。理由は3点。① ドメインモデル Notification が既に集約であり、updateNotification(n) は集約全体の置換を契約とする。② SharePoint にはリスト横断トランザクションが無い。子を6リストに割ると1回の保存が非原子的になり、採番・XML生成の前提が壊れる。集約JSONなら常に「1アイテム1書き込み＝原子的」。③ リストのバージョン管理がそのまま「届のスナップショット履歴」として機能する。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>(3) 日付は SharePoint 日付型を使わず YYYY-MM-DD 文字列で保持</t>
+          <t>(2) 昇格列は投影であって正本ではない</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>タイムゾーン変換による日付ずれを回避するため。届出年月日・提出期限・変更年月日など、法令上の「日」がずれると30日調査・提出期限の判断を誤る。ソート・フィルタは ISO 文字列の辞書順で正しく機能する。</t>
+          <t>CtnPayload（集約JSON）が正本。昇格列は一覧表示・フィルタ・ダッシュボード集計のための投影。保存時に Payload と昇格列を必ず同一の書き込みで更新する（別々に更新しない）。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>(4) 列内部名は Ctn プレフィックス必須</t>
+          <t>(3) 日付は SharePoint 日付型を使わず YYYY-MM-DD 文字列で保持</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Title / Status / Order / Owner / Created 等の SharePoint 予約名との衝突を避ける。参照列の書き込みは {内部名}Id を使う。</t>
+          <t>タイムゾーン変換による日付ずれを回避するため。届出年月日・提出期限・変更年月日など、法令上の「日」がずれると30日調査・提出期限の判断を誤る。ソート・フィルタは ISO 文字列の辞書順で正しく機能する。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>(5) 物理削除しない（論理削除）</t>
+          <t>(4) 列内部名は Ctn プレフィックス必須</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>マスタは CtnActive（はい/いいえ）で無効化し履歴を保持。医師の同一性キー（CtnDoctors のアイテムID）は改名しても不変。届は下書きのみ削除可、提出済は削除不可。</t>
+          <t>Title / Status / Order / Owner / Created 等の SharePoint 予約名との衝突を避ける。参照列の書き込みは {内部名}Id を使う。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>(6) 選択肢の格納方式</t>
+          <t>(5) 物理削除しない（論理削除）</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>数値 enum（Dataverse の 100000xxx 系コード値）は数値列に保持し、ラベルは ctn-schema.json から引く（ハードコード禁止）。文字列 union（notifType / status / role）は SharePoint 選択肢列にして標準UIでも絞り込めるようにする。</t>
+          <t>マスタは CtnActive（はい/いいえ）で無効化し履歴を保持。医師の同一性キー（CtnDoctors のアイテムID）は改名しても不変。届は下書きのみ削除可、提出済は削除不可。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>(6) 選択肢の格納方式</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>数値 enum（Dataverse の 100000xxx 系コード値）は数値列に保持し、ラベルは ctn-schema.json から引く（ハードコード禁止）。文字列 union（notifType / status / role）は SharePoint 選択肢列にして標準UIでも絞り込めるようにする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>(7) ドメインID とアイテムID</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>SharePoint のアイテム ID（数値）を String() 化してドメインの文字列 id とする。変換はリポジトリ境界で完結させ UI へ漏らさない。</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>3. 二層検証（サーバー正本）の扱い — 最大のトレードオフ</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>問題</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>本来の設計思想は「クライアント＝提案のみ、確定＝サーバー」。Dataverse 構想では serverLogic 16件をプラグインが強制する。SPFx はブラウザ内でのみ実行されるため、この意味での「サーバー」が存在しない。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>受け入れる前提</t>
+          <t>問題</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>採番・職務分離・提出ゲートの強制はリポジトリ層（ブラウザ内）で行う。これは意図的なトレードオフとして受け入れる。</t>
+          <t>本来の設計思想は「クライアント＝提案のみ、確定＝サーバー」。Dataverse 構想では serverLogic 16件をプラグインが強制する。SPFx はブラウザ内でのみ実行されるため、この意味での「サーバー」が存在しない。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>緩和策1: 書き込み経路の一本化</t>
+          <t>受け入れる前提</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>全書き込みを SharePointCtnRepository に集約し、保存・承認・提出で logic.ts の検証を必ず再実行する</t>
+          <t>採番・職務分離・提出ゲートの強制はリポジトリ層（ブラウザ内）で行う。これは意図的なトレードオフとして受け入れる。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>緩和策2: 楽観的同時実行制御</t>
+          <t>緩和策1: 書き込み経路の一本化</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>更新は取得時 etag の IF-MATCH（'*' 禁止）。412 Precondition Failed は再取得して競合をユーザーに提示。特に提出時の順序番号確定は「同一シリーズの最新届を再取得 → 再計算 → etag付き書き込み → 412ならリトライ」ループで衝突を排除する</t>
+          <t>全書き込みを SharePointCtnRepository に集約し、保存・承認・提出で logic.ts の検証を必ず再実行する</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>緩和策3: リスト直編集の統制</t>
+          <t>緩和策2: 楽観的同時実行制御</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>サイトナビゲーションからリストを隠す／編集権限を利用メンバーに限定／バージョン管理で事後検知。厳密な強制が必要になった時点が Dataverse 移行の判断トリガー</t>
+          <t>更新は取得時 etag の IF-MATCH（'*' 禁止）。412 Precondition Failed は再取得して競合をユーザーに提示。特に提出時の順序番号確定は「同一シリーズの最新届を再取得 → 再計算 → etag付き書き込み → 412ならリトライ」ループで衝突を排除する</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>緩和策3: リスト直編集の統制</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>サイトナビゲーションからリストを隠す／編集権限を利用メンバーに限定／バージョン管理で事後検知。厳密な強制が必要になった時点が Dataverse 移行の判断トリガー</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
           <t>残余リスク</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>サイト権限を持つ利用者は SharePoint 標準UIからリストを直接編集でき、アプリの検証を迂回しうる（運用で緩和）</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>4. 本設計で新規に追加したリスト（demo/app には対応する永続化が無い）</t>
-        </is>
-      </c>
-    </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>CtnSettings</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>rules.ts の RuleSettings（提出期限オフセット・アラート閾値・有効/無効）は現状メモリ内シングルトンでリロード時に既定へ戻る。バックエンド化にあたり単一アイテムのリストとして永続化する。全利用者で共有される設定のため、更新は薬事担当ロールに限定する。</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>4. PDF / XML 出力の位置づけ（2026-07-26 追記）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CtnAppUsers</t>
+          <t>現行実装</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>職務分離（起票者≠承認者）の判定にはロール（起票/レビュー/承認/薬事）が必要。actor 自体は pageContext から取るが、ロールの正本が無いと承認可否を判定できないため loginName → ロールの登録簿を持つ。SharePoint グループでの代替も可能だが、UI がロールラベルを表示する都合上リスト方式を推奨。</t>
+          <t>ブランチ claude/ctn-output-pdf-xml を main へマージ済み。届出詳細の［提出パッケージ出力］で ① CTN XML（xml.ts）② 届書PDF（output.ts: html2canvas でラスタライズ → pdf-lib でページ化）を生成し、添付「検査キット/パッキングリスト」があれば実PDFを結合して1ファイル化する。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>★用途の切り分け（重要）</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>現行の届書PDFは【社内レビュー用】。PMDA への提出正本は XML（＋添付PDF）である。ただし PMDA 提出用PDFは最終的に必須となる見込みであり、その段階では要件が変わる（下記）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>現行方式の制約</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>① ラスタライズ方式のため PDF 内のテキストが選択・検索・コピーできない。② ページ分割が画像のオフセットずらしのため、表や行がページ境界で切断されうる。③ html2canvas + pdf-lib によりバンドルが増加（demo/index.html が約450KB → 約1,081KB）。社内レビュー用途では許容できるが、提出用途では①が問題になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>★設計上の整合性リスク</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>ctn-schema.json の添付資料テーブルには cr_hastext（テキスト含有チェック）と cr_hasbookmarks（しおり付与チェック）があり、これは PMDA の PDF 品質要件に対応する。ラスタライズPDFはテキストを含まないため、提出用途へ格上げする際は必ず方式の見直しが必要になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>提出用途へ格上げする場合の方式</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Word テンプレート＋SharePoint/OneDrive の「ファイルの変換」アクション（標準コネクタのため追加費用なし）によるサーバー側生成を推奨。様式の再現度が高く、テキスト選択可・日本語フォント問題なしを同時に満たす。pdf-lib への日本語フォント埋め込みは Noto Sans JP でバンドルが数MB増えるため SPFx では割に合わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>本設計への影響（いずれも追記のみ・既存定義は不変）</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>① CtnNotifications に CtnPdfGeneratedAt を1列追加（CtnXmlGeneratedAt と対称）。② 生成物の保管先として CtnGeneratedOutputs ドキュメントライブラリを追加。③ 06_ロジック実装マップ に「届書PDF生成」「提出パッケージ結合」の2件を追加。④ 07_画面データ連携 に「提出パッケージ出力」を追加。データモデル本体（CtnPayload の構造）は変更不要。PDF は Payload からの出力にすぎないため。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>CtnAttachmentFiles の段階</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>現行は添付のメタデータのみを Payload に保持し、実ファイルは持たない（デモはサンプルPDFを生成して結合）。★実ファイル結合を本番で行う段階（＝提出用途への格上げ時）に CtnAttachmentFiles が必須となる。社内レビュー用途に留まる限りは将来フェーズのままでよい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>5. 本設計で新規に追加したリスト（demo/app には対応する永続化が無い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>CtnSettings</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>rules.ts の RuleSettings（提出期限オフセット・アラート閾値・有効/無効）は現状メモリ内シングルトンでリロード時に既定へ戻る。バックエンド化にあたり単一アイテムのリストとして永続化する。全利用者で共有される設定のため、更新は薬事担当ロールに限定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>CtnAppUsers</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>職務分離（起票者≠承認者）の判定にはロール（起票/レビュー/承認/薬事）が必要。actor 自体は pageContext から取るが、ロールの正本が無いと承認可否を判定できないため loginName → ロールの登録簿を持つ。SharePoint グループでの代替も可能だが、UI がロールラベルを表示する都合上リスト方式を推奨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
           <t>CtnAttachmentFiles</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>現アプリの添付はメタデータのみ（実ファイルは持たない）。実ファイル格納はドキュメントライブラリとして将来フェーズで追加する。本設計では列定義のみ記載し、Phase 1 のスコープ外とする。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1194,7 +1298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2691,8 +2795,92 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>（横断）</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>PMDA 提出用PDFの要件</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>CtnGeneratedOutputs.CtnOutputKind = pdf-submission</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>内部管理（PDF品質要件）</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>★PDF出力は最終的に PMDA へ必須となる見込み。現行の届書PDFは社内レビュー用（ラスタライズ・テキスト非選択）。提出用に求められる要件（テキスト選択可・しおり付与・様式の再現度）を確定させ、サーバー側生成（Word テンプレート＋ファイル変換）へ切り替える時期を判断する</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>（横断）</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>検査キット/パッキングリストの実ファイル結合</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>CtnAttachmentFiles</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>現行はデモ用サンプルPDFを生成して結合。本番で実ファイルを結合する運用に移す時期と、その前提となる CtnAttachmentFiles の構築時期を確定させる</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:H39"/>
+  <autoFilter ref="A5:H41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2703,7 +2891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3416,7 +3604,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Protocol / IB / ICF 等の実ファイル格納</t>
+          <t>Protocol / IB / ICF / 検査キット・パッキングリスト 等の実ファイル格納</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
@@ -3446,12 +3634,69 @@
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>将来フェーズ（Phase 1 スコープ外）</t>
+          <t>将来フェーズ。★提出パッケージで実ファイルを結合する段階（提出用途への格上げ時）に必須化する</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>13★</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>CtnGeneratedOutputs</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>生成物</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ドキュメントライブラリ</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>提出パッケージ出力の生成物（届書PDF・CTN XML）の保管</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>生成物（正本は CtnPayload）</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>数百〜2,000</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>生成時に自動アップロード（上書きせず版を積む）</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>—（新規）</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>既存の SharePoint 文書設計（Source PDFs / Attachments / Generated Outputs の3ライブラリ構成）へ寄せる</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K16"/>
+  <autoFilter ref="A4:K17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3462,7 +3707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4417,44 +4662,36 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>CtnPayload</t>
+          <t>CtnPdfGeneratedAt</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>集約ペイロード</t>
+          <t>届書PDF生成日時</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>複数行（プレーン）</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>単一行</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr"/>
       <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
+      <c r="G26" s="7" t="inlineStr"/>
       <c r="H26" s="7" t="inlineStr"/>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>ISO8601</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>Notification 全体</t>
+          <t>（新規）</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>★正本。子配列（studyDrugs / sites / attachments / references / inquiries）を内包。リッチテキストにしない（HTMLエスケープでJSONが壊れる）</t>
+          <t>提出パッケージ出力の実行日時。CtnXmlGeneratedAt と対称に持つ。現行の届書PDFは社内レビュー用（ラスタライズ方式）</t>
         </is>
       </c>
     </row>
@@ -4466,17 +4703,17 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>CtnPayloadVersion</t>
+          <t>CtnPayload</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>ペイロード版</t>
+          <t>集約ペイロード</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>複数行（プレーン）</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -4485,21 +4722,25 @@
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>（メタ）</t>
+          <t>Notification 全体</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>将来のスキーマ移行用。リポジトリ内でマイグレーション分岐</t>
+          <t>★正本。子配列（studyDrugs / sites / attachments / references / inquiries）を内包。リッチテキストにしない（HTMLエスケープでJSONが壊れる）</t>
         </is>
       </c>
     </row>
@@ -4511,58 +4752,62 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Modified / Editor</t>
+          <t>CtnPayloadVersion</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>更新日時 / 更新者</t>
+          <t>ペイロード版</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>標準列</t>
+          <t>単一行</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>自動</t>
+          <t>○</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
       <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I28" s="8" t="inlineStr"/>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>（メタ）</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>SharePoint 標準。楽観ロックの etag と併用</t>
+          <t>将来のスキーマ移行用。リポジトリ内でマイグレーション分岐</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>CtnCompounds</t>
+          <t>CtnNotifications</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Modified / Editor</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>アイテムID</t>
+          <t>更新日時 / 更新者</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>数値（標準）</t>
+          <t>標準列</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -4570,26 +4815,18 @@
           <t>自動</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>自動</t>
-        </is>
-      </c>
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
       <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="8" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>ドメイン id</t>
+          <t>SharePoint 標準。楽観ロックの etag と併用</t>
         </is>
       </c>
     </row>
@@ -4601,48 +4838,44 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>治験成分記号</t>
+          <t>アイテムID</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>数値（標準）</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>自動</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>半角英数字＋ハイフン・20桁以内・「&amp;」不可</t>
-        </is>
-      </c>
+      <c r="I30" s="8" t="inlineStr"/>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>compoundCode</t>
+          <t>id</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>★validateCompoundCode() で検証。スペース有無で別記号と判定される</t>
+          <t>ドメイン id</t>
         </is>
       </c>
     </row>
@@ -4654,17 +4887,17 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>CtnTargetCategory</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>対象区分</t>
+          <t>治験成分記号</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>数値</t>
+          <t>単一行</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -4672,24 +4905,32 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>100000100</t>
-        </is>
-      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr"/>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>医薬品/医療機器/再生医療等製品</t>
+          <t>半角英数字＋ハイフン・20桁以内・「&amp;」不可</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>targetCategory</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="inlineStr"/>
+          <t>compoundCode</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>★validateCompoundCode() で検証。スペース有無で別記号と判定される</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -4699,17 +4940,17 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>CtnTrialKind</t>
+          <t>CtnTargetCategory</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>治験の種類</t>
+          <t>対象区分</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>数値</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -4719,11 +4960,19 @@
       </c>
       <c r="F32" s="7" t="inlineStr"/>
       <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="8" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>100000100</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>医薬品/医療機器/再生医療等製品</t>
+        </is>
+      </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>trialKind</t>
+          <t>targetCategory</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr"/>
@@ -4736,12 +4985,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>CtnInitReceptNo</t>
+          <t>CtnTrialKind</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>初回届出受付番号</t>
+          <t>治験の種類</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -4749,14 +4998,18 @@
           <t>単一行</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr"/>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F33" s="7" t="inlineStr"/>
       <c r="G33" s="7" t="inlineStr"/>
       <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="8" t="inlineStr"/>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>initReceptNo</t>
+          <t>trialKind</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr"/>
@@ -4769,12 +5022,12 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>CtnInitNoteDate</t>
+          <t>CtnInitReceptNo</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>初回届出年月日</t>
+          <t>初回届出受付番号</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -4786,21 +5039,13 @@
       <c r="F34" s="7" t="inlineStr"/>
       <c r="G34" s="7" t="inlineStr"/>
       <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
+      <c r="I34" s="8" t="inlineStr"/>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>initNoteDate</t>
-        </is>
-      </c>
-      <c r="K34" s="8" t="inlineStr">
-        <is>
-          <t>30日調査の起算日</t>
-        </is>
-      </c>
+          <t>initReceptNo</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -4810,48 +5055,36 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>CtnDevStatus</t>
+          <t>CtnInitNoteDate</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>開発状態</t>
+          <t>初回届出年月日</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>単一行</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr"/>
       <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>100000900</t>
-        </is>
-      </c>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>開発中 / 開発中止</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>devStatus</t>
+          <t>initNoteDate</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>★開発中止届の提出で自動的に「開発中止」へ遷移</t>
+          <t>30日調査の起算日</t>
         </is>
       </c>
     </row>
@@ -4863,17 +5096,17 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>CtnSponsor</t>
+          <t>CtnDevStatus</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>主たる届出者</t>
+          <t>開発状態</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>参照（CtnSponsors）</t>
+          <t>数値</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -4882,17 +5115,29 @@
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="8" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>100000900</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>開発中 / 開発中止</t>
+        </is>
+      </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>sponsorId</t>
+          <t>devStatus</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>Dataverse 構想の cr_compound には無い列。UI が保持するため追加</t>
+          <t>★開発中止届の提出で自動的に「開発中止」へ遷移</t>
         </is>
       </c>
     </row>
@@ -4904,32 +5149,36 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>CtnDrugName</t>
+          <t>CtnSponsor</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>代表的な被験薬名称</t>
+          <t>主たる届出者</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr"/>
+          <t>参照（CtnSponsors）</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F37" s="7" t="inlineStr"/>
       <c r="G37" s="7" t="inlineStr"/>
       <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>drugName</t>
+          <t>sponsorId</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>表示用</t>
+          <t>Dataverse 構想の cr_compound には無い列。UI が保持するため追加</t>
         </is>
       </c>
     </row>
@@ -4941,12 +5190,12 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>CtnCreatedAt</t>
+          <t>CtnDrugName</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>代表的な被験薬名称</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -4958,59 +5207,51 @@
       <c r="F38" s="7" t="inlineStr"/>
       <c r="G38" s="7" t="inlineStr"/>
       <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="I38" s="8" t="inlineStr"/>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>createdAt</t>
-        </is>
-      </c>
-      <c r="K38" s="8" t="inlineStr"/>
+          <t>drugName</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>表示用</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>CtnSponsors</t>
+          <t>CtnCompounds</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CtnCreatedAt</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>アイテムID</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>数値（標準）</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>自動</t>
-        </is>
-      </c>
+          <t>単一行</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr"/>
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr"/>
       <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>createdAt</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr"/>
@@ -5023,35 +5264,39 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>届出者の名称</t>
+          <t>アイテムID</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>数値（標準）</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr"/>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>自動</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr"/>
       <c r="I40" s="8" t="inlineStr"/>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr"/>
@@ -5064,12 +5309,12 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>CtnSponsorType</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>届出者の種別</t>
+          <t>届出者の名称</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -5083,12 +5328,16 @@
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="8" t="inlineStr"/>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>sponsorType</t>
+          <t>name</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr"/>
@@ -5101,12 +5350,12 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>CtnRepName</t>
+          <t>CtnSponsorType</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>代表者の氏名</t>
+          <t>届出者の種別</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -5125,14 +5374,10 @@
       <c r="I42" s="8" t="inlineStr"/>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>repName</t>
-        </is>
-      </c>
-      <c r="K42" s="8" t="inlineStr">
-        <is>
-          <t>変更時は変更届（変更後6ヶ月以内）の対象</t>
-        </is>
-      </c>
+          <t>sponsorType</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -5142,12 +5387,12 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>CtnAddress1</t>
+          <t>CtnRepName</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>所在地1</t>
+          <t>代表者の氏名</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -5166,10 +5411,14 @@
       <c r="I43" s="8" t="inlineStr"/>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>address1</t>
-        </is>
-      </c>
-      <c r="K43" s="8" t="inlineStr"/>
+          <t>repName</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>変更時は変更届（変更後6ヶ月以内）の対象</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -5179,12 +5428,12 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>CtnAddress2</t>
+          <t>CtnAddress1</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>所在地2</t>
+          <t>所在地1</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -5192,14 +5441,18 @@
           <t>単一行</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr"/>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F44" s="7" t="inlineStr"/>
       <c r="G44" s="7" t="inlineStr"/>
       <c r="H44" s="7" t="inlineStr"/>
       <c r="I44" s="8" t="inlineStr"/>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>address2</t>
+          <t>address1</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr"/>
@@ -5212,12 +5465,12 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>CtnManufacturerCode</t>
+          <t>CtnAddress2</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>業者コード</t>
+          <t>所在地2</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -5225,22 +5478,14 @@
           <t>単一行</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="E45" s="7" t="inlineStr"/>
       <c r="F45" s="7" t="inlineStr"/>
       <c r="G45" s="7" t="inlineStr"/>
       <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>コード表</t>
-        </is>
-      </c>
+      <c r="I45" s="8" t="inlineStr"/>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>manufacturerCode</t>
+          <t>address2</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr"/>
@@ -5253,12 +5498,12 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>CtnContactName</t>
+          <t>CtnManufacturerCode</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>届出担当者の氏名</t>
+          <t>業者コード</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -5274,10 +5519,14 @@
       <c r="F46" s="7" t="inlineStr"/>
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>コード表</t>
+        </is>
+      </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>contactName</t>
+          <t>manufacturerCode</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr"/>
@@ -5290,12 +5539,12 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>CtnContactTitle</t>
+          <t>CtnContactName</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>届出担当者の所属</t>
+          <t>届出担当者の氏名</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -5314,7 +5563,7 @@
       <c r="I47" s="8" t="inlineStr"/>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>contactTitle</t>
+          <t>contactName</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr"/>
@@ -5327,12 +5576,12 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>CtnTelNo</t>
+          <t>CtnContactTitle</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>届出担当者の所属</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -5351,7 +5600,7 @@
       <c r="I48" s="8" t="inlineStr"/>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>telNo</t>
+          <t>contactTitle</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr"/>
@@ -5364,12 +5613,12 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>CtnFaxOrMail</t>
+          <t>CtnTelNo</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>FAX番号又はメールアドレス</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -5388,141 +5637,133 @@
       <c r="I49" s="8" t="inlineStr"/>
       <c r="J49" s="7" t="inlineStr">
         <is>
+          <t>telNo</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>CtnSponsors</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>CtnFaxOrMail</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>FAX番号又はメールアドレス</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>単一行</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr"/>
+      <c r="G50" s="7" t="inlineStr"/>
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="8" t="inlineStr"/>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
           <t>faxOrMail</t>
         </is>
       </c>
-      <c r="K49" s="8" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="K50" s="8" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>CtnSponsors</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>CtnOverseasInfo</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>海外依頼者・外国製造業者情報</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>複数行</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr"/>
-      <c r="F50" s="12" t="inlineStr"/>
-      <c r="G50" s="12" t="inlineStr"/>
-      <c r="H50" s="12" t="inlineStr"/>
-      <c r="I50" s="14" t="inlineStr"/>
-      <c r="J50" s="12" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr"/>
+      <c r="F51" s="12" t="inlineStr"/>
+      <c r="G51" s="12" t="inlineStr"/>
+      <c r="H51" s="12" t="inlineStr"/>
+      <c r="I51" s="14" t="inlineStr"/>
+      <c r="J51" s="12" t="inlineStr">
         <is>
           <t>overseasInfo</t>
         </is>
       </c>
-      <c r="K50" s="14" t="inlineStr">
+      <c r="K51" s="14" t="inlineStr">
         <is>
           <t>⚠要確認（邦文4項目＋外国文4項目の構造を手引き・XSDと突合して確定させる）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>CtnSponsors</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>CtnActive</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>有効</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>はい/いいえ</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr"/>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>はい</t>
-        </is>
-      </c>
-      <c r="I51" s="8" t="inlineStr"/>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="K51" s="8" t="inlineStr">
-        <is>
-          <t>論理削除（物理削除しない）</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>CtnInstitutions</t>
+          <t>CtnSponsors</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CtnActive</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>アイテムID</t>
+          <t>有効</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>数値（標準）</t>
+          <t>はい/いいえ</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
           <t>○</t>
         </is>
       </c>
+      <c r="F52" s="7" t="inlineStr"/>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr"/>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
       <c r="I52" s="8" t="inlineStr"/>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="K52" s="8" t="inlineStr"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>論理削除（物理削除しない）</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -5532,35 +5773,39 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>機関名称</t>
+          <t>アイテムID</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>数値（標準）</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr"/>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>自動</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="8" t="inlineStr"/>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr"/>
@@ -5573,12 +5818,12 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>CtnCode</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>機関コード</t>
+          <t>機関名称</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -5591,11 +5836,7 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="F54" s="7" t="inlineStr"/>
       <c r="G54" s="7" t="inlineStr">
         <is>
           <t>○</t>
@@ -5605,14 +5846,10 @@
       <c r="I54" s="8" t="inlineStr"/>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="K54" s="8" t="inlineStr">
-        <is>
-          <t>表示用の一意コード</t>
-        </is>
-      </c>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -5622,12 +5859,12 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>CtnAddress1</t>
+          <t>CtnCode</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>所在地1</t>
+          <t>機関コード</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -5640,16 +5877,28 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr"/>
-      <c r="G55" s="7" t="inlineStr"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="8" t="inlineStr"/>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>address1</t>
-        </is>
-      </c>
-      <c r="K55" s="8" t="inlineStr"/>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="K55" s="8" t="inlineStr">
+        <is>
+          <t>表示用の一意コード</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -5659,12 +5908,12 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>CtnAddress2</t>
+          <t>CtnAddress1</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>所在地2</t>
+          <t>所在地1</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -5672,14 +5921,18 @@
           <t>単一行</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr"/>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F56" s="7" t="inlineStr"/>
       <c r="G56" s="7" t="inlineStr"/>
       <c r="H56" s="7" t="inlineStr"/>
       <c r="I56" s="8" t="inlineStr"/>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>address2</t>
+          <t>address1</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr"/>
@@ -5692,12 +5945,12 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>CtnTelNo</t>
+          <t>CtnAddress2</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>代表電話番号</t>
+          <t>所在地2</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -5705,18 +5958,14 @@
           <t>単一行</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="E57" s="7" t="inlineStr"/>
       <c r="F57" s="7" t="inlineStr"/>
       <c r="G57" s="7" t="inlineStr"/>
       <c r="H57" s="7" t="inlineStr"/>
       <c r="I57" s="8" t="inlineStr"/>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>telNo</t>
+          <t>address2</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr"/>
@@ -5729,17 +5978,17 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>CtnActive</t>
+          <t>CtnTelNo</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>有効</t>
+          <t>代表電話番号</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>はい/いいえ</t>
+          <t>単一行</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -5748,74 +5997,62 @@
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>はい</t>
-        </is>
-      </c>
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr"/>
       <c r="I58" s="8" t="inlineStr"/>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="K58" s="8" t="inlineStr">
-        <is>
-          <t>論理削除で履歴保持</t>
-        </is>
-      </c>
+          <t>telNo</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>CtnDoctors</t>
+          <t>CtnInstitutions</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CtnActive</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>アイテムID</t>
+          <t>有効</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>数値（標準）</t>
+          <t>はい/いいえ</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
           <t>○</t>
         </is>
       </c>
+      <c r="F59" s="7" t="inlineStr"/>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr"/>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
       <c r="I59" s="8" t="inlineStr"/>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>★不変の同一性キー。改名しても不変（アイテムを作り直さない）</t>
+          <t>論理削除で履歴保持</t>
         </is>
       </c>
     </row>
@@ -5827,40 +6064,44 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>氏名（原表記）</t>
+          <t>アイテムID</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>数値（標準）</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr"/>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>自動</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="8" t="inlineStr"/>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>nameOriginal</t>
+          <t>id</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>外字を含みうる元の表記</t>
+          <t>★不変の同一性キー。改名しても不変（アイテムを作り直さない）</t>
         </is>
       </c>
     </row>
@@ -5872,12 +6113,12 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>CtnDoctorNo</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>医師表示ID</t>
+          <t>氏名（原表記）</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -5890,11 +6131,7 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="F61" s="7" t="inlineStr"/>
       <c r="G61" s="7" t="inlineStr">
         <is>
           <t>○</t>
@@ -5904,12 +6141,12 @@
       <c r="I61" s="8" t="inlineStr"/>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>doctorNo</t>
+          <t>nameOriginal</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>自動採番（Dataverse のオートナンバー相当をリポジトリ層で実装）</t>
+          <t>外字を含みうる元の表記</t>
         </is>
       </c>
     </row>
@@ -5921,12 +6158,12 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>CtnNameFiling</t>
+          <t>CtnDoctorNo</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>氏名（届出用表記）</t>
+          <t>医師表示ID</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -5939,18 +6176,26 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr"/>
-      <c r="G62" s="7" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="8" t="inlineStr"/>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>nameFiling</t>
+          <t>doctorNo</t>
         </is>
       </c>
       <c r="K62" s="8" t="inlineStr">
         <is>
-          <t>★外字正規化済み。XML に出力されるのはこちら</t>
+          <t>自動採番（Dataverse のオートナンバー相当をリポジトリ層で実装）</t>
         </is>
       </c>
     </row>
@@ -5962,12 +6207,12 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>CtnPronounce</t>
+          <t>CtnNameFiling</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>よみかな</t>
+          <t>氏名（届出用表記）</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -5983,19 +6228,15 @@
       <c r="F63" s="7" t="inlineStr"/>
       <c r="G63" s="7" t="inlineStr"/>
       <c r="H63" s="7" t="inlineStr"/>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>全角50字（100バイト）以内</t>
-        </is>
-      </c>
+      <c r="I63" s="8" t="inlineStr"/>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>pronounce</t>
+          <t>nameFiling</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr">
         <is>
-          <t>★checkByteLimit() の対象</t>
+          <t>★外字正規化済み。XML に出力されるのはこちら</t>
         </is>
       </c>
     </row>
@@ -6007,12 +6248,12 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>CtnMedSchoolNo</t>
+          <t>CtnPronounce</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>大学番号</t>
+          <t>よみかな</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -6030,17 +6271,17 @@
       <c r="H64" s="7" t="inlineStr"/>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>コード表</t>
+          <t>全角50字（100バイト）以内</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>medSchoolNo</t>
+          <t>pronounce</t>
         </is>
       </c>
       <c r="K64" s="8" t="inlineStr">
         <is>
-          <t>責任医師想定</t>
+          <t>★checkByteLimit() の対象</t>
         </is>
       </c>
     </row>
@@ -6052,12 +6293,12 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>CtnGraduationYear</t>
+          <t>CtnMedSchoolNo</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>卒業年</t>
+          <t>大学番号</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -6073,13 +6314,21 @@
       <c r="F65" s="7" t="inlineStr"/>
       <c r="G65" s="7" t="inlineStr"/>
       <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="8" t="inlineStr"/>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>コード表</t>
+        </is>
+      </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>graduationYear</t>
-        </is>
-      </c>
-      <c r="K65" s="8" t="inlineStr"/>
+          <t>medSchoolNo</t>
+        </is>
+      </c>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>責任医師想定</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -6089,17 +6338,17 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>CtnHasGaiji</t>
+          <t>CtnGraduationYear</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>外字有無</t>
+          <t>卒業年</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>はい/いいえ</t>
+          <t>単一行</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
@@ -6108,27 +6357,15 @@
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>いいえ</t>
-        </is>
-      </c>
+      <c r="G66" s="7" t="inlineStr"/>
+      <c r="H66" s="7" t="inlineStr"/>
       <c r="I66" s="8" t="inlineStr"/>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>hasGaiji</t>
-        </is>
-      </c>
-      <c r="K66" s="8" t="inlineStr">
-        <is>
-          <t>detectGaiji() の検出結果。真なら届出前に確認ダイアログを必須にする</t>
-        </is>
-      </c>
+          <t>graduationYear</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -6138,32 +6375,44 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>CtnInstitution</t>
+          <t>CtnHasGaiji</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>主たる所属医療機関</t>
+          <t>外字有無</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>参照（CtnInstitutions）</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr"/>
+          <t>はい/いいえ</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F67" s="7" t="inlineStr"/>
-      <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
       <c r="I67" s="8" t="inlineStr"/>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>institutionId</t>
+          <t>hasGaiji</t>
         </is>
       </c>
       <c r="K67" s="8" t="inlineStr">
         <is>
-          <t>運用・表示用（XML対象外）</t>
+          <t>detectGaiji() の検出結果。真なら届出前に確認ダイアログを必須にする</t>
         </is>
       </c>
     </row>
@@ -6175,84 +6424,76 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>CtnActive</t>
+          <t>CtnInstitution</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>有効</t>
+          <t>主たる所属医療機関</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>はい/いいえ</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>参照（CtnInstitutions）</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr"/>
       <c r="F68" s="7" t="inlineStr"/>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>はい</t>
-        </is>
-      </c>
+      <c r="G68" s="7" t="inlineStr"/>
+      <c r="H68" s="7" t="inlineStr"/>
       <c r="I68" s="8" t="inlineStr"/>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="K68" s="8" t="inlineStr"/>
+          <t>institutionId</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>運用・表示用（XML対象外）</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>CtnSiteStaff</t>
+          <t>CtnDoctors</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CtnActive</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>アイテムID</t>
+          <t>有効</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>数値（標準）</t>
+          <t>はい/いいえ</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
           <t>○</t>
         </is>
       </c>
+      <c r="F69" s="7" t="inlineStr"/>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="H69" s="7" t="inlineStr"/>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
       <c r="I69" s="8" t="inlineStr"/>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K69" s="8" t="inlineStr"/>
@@ -6265,31 +6506,39 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>氏名</t>
+          <t>アイテムID</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>数値（標準）</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr"/>
-      <c r="G70" s="7" t="inlineStr"/>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
       <c r="H70" s="7" t="inlineStr"/>
       <c r="I70" s="8" t="inlineStr"/>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="K70" s="8" t="inlineStr"/>
@@ -6302,12 +6551,12 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>CtnKana</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>よみかな</t>
+          <t>氏名</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -6315,14 +6564,18 @@
           <t>単一行</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr"/>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F71" s="7" t="inlineStr"/>
       <c r="G71" s="7" t="inlineStr"/>
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="8" t="inlineStr"/>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>kana</t>
+          <t>name</t>
         </is>
       </c>
       <c r="K71" s="8" t="inlineStr"/>
@@ -6335,39 +6588,27 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>CtnRole</t>
+          <t>CtnKana</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>役割</t>
+          <t>よみかな</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>選択肢</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>単一行</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr"/>
       <c r="G72" s="7" t="inlineStr"/>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>CRC</t>
-        </is>
-      </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>CRC / 事務局 / 薬剤部</t>
-        </is>
-      </c>
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="8" t="inlineStr"/>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>kana</t>
         </is>
       </c>
       <c r="K72" s="8" t="inlineStr"/>
@@ -6380,17 +6621,17 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>CtnInstitution</t>
+          <t>CtnRole</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>所属医療機関</t>
+          <t>役割</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>参照（CtnInstitutions）</t>
+          <t>選択肢</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
@@ -6399,16 +6640,20 @@
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr"/>
-      <c r="I73" s="8" t="inlineStr"/>
+      <c r="G73" s="7" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>CRC</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>CRC / 事務局 / 薬剤部</t>
+        </is>
+      </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>institutionId</t>
+          <t>role</t>
         </is>
       </c>
       <c r="K73" s="8" t="inlineStr"/>
@@ -6421,27 +6666,35 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>CtnTelNo</t>
+          <t>CtnInstitution</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>所属医療機関</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr"/>
+          <t>参照（CtnInstitutions）</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F74" s="7" t="inlineStr"/>
-      <c r="G74" s="7" t="inlineStr"/>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="H74" s="7" t="inlineStr"/>
       <c r="I74" s="8" t="inlineStr"/>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>telNo</t>
+          <t>institutionId</t>
         </is>
       </c>
       <c r="K74" s="8" t="inlineStr"/>
@@ -6454,12 +6707,12 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>CtnMail</t>
+          <t>CtnTelNo</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>メールアドレス</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -6474,7 +6727,7 @@
       <c r="I75" s="8" t="inlineStr"/>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>telNo</t>
         </is>
       </c>
       <c r="K75" s="8" t="inlineStr"/>
@@ -6487,91 +6740,79 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>CtnActive</t>
+          <t>CtnMail</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>有効</t>
+          <t>メールアドレス</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>はい/いいえ</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>単一行</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr"/>
       <c r="F76" s="7" t="inlineStr"/>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>はい</t>
-        </is>
-      </c>
+      <c r="G76" s="7" t="inlineStr"/>
+      <c r="H76" s="7" t="inlineStr"/>
       <c r="I76" s="8" t="inlineStr"/>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="K76" s="8" t="inlineStr">
-        <is>
-          <t>XML対象外・運用連絡先</t>
-        </is>
-      </c>
+          <t>mail</t>
+        </is>
+      </c>
+      <c r="K76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>CtnIrbs</t>
+          <t>CtnSiteStaff</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CtnActive</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>アイテムID</t>
+          <t>有効</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>数値（標準）</t>
+          <t>はい/いいえ</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
           <t>○</t>
         </is>
       </c>
+      <c r="F77" s="7" t="inlineStr"/>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="H77" s="7" t="inlineStr"/>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
       <c r="I77" s="8" t="inlineStr"/>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="K77" s="8" t="inlineStr"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K77" s="8" t="inlineStr">
+        <is>
+          <t>XML対象外・運用連絡先</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -6581,35 +6822,39 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>設置者の名称</t>
+          <t>アイテムID</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>数値（標準）</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr"/>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>自動</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="8" t="inlineStr"/>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>ownerName</t>
+          <t>id</t>
         </is>
       </c>
       <c r="K78" s="8" t="inlineStr"/>
@@ -6622,17 +6867,17 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>CtnIrbType</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>院内・外部の区分</t>
+          <t>設置者の名称</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>数値</t>
+          <t>単一行</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
@@ -6641,20 +6886,16 @@
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
-      <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr">
-        <is>
-          <t>100001400</t>
-        </is>
-      </c>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>院内 / 外部</t>
-        </is>
-      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr"/>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>irbType</t>
+          <t>ownerName</t>
         </is>
       </c>
       <c r="K79" s="8" t="inlineStr"/>
@@ -6667,17 +6908,17 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>CtnAddress1</t>
+          <t>CtnIrbType</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>所在地1</t>
+          <t>院内・外部の区分</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>数値</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -6687,11 +6928,19 @@
       </c>
       <c r="F80" s="7" t="inlineStr"/>
       <c r="G80" s="7" t="inlineStr"/>
-      <c r="H80" s="7" t="inlineStr"/>
-      <c r="I80" s="8" t="inlineStr"/>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>100001400</t>
+        </is>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>院内 / 外部</t>
+        </is>
+      </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>address1</t>
+          <t>irbType</t>
         </is>
       </c>
       <c r="K80" s="8" t="inlineStr"/>
@@ -6704,23 +6953,31 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>CtnAddress2</t>
+          <t>CtnAddress1</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>所在地2</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr"/>
-      <c r="E81" s="7" t="inlineStr"/>
+          <t>所在地1</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>単一行</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F81" s="7" t="inlineStr"/>
       <c r="G81" s="7" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="8" t="inlineStr"/>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>address2</t>
+          <t>address1</t>
         </is>
       </c>
       <c r="K81" s="8" t="inlineStr"/>
@@ -6733,39 +6990,23 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>CtnActive</t>
+          <t>CtnAddress2</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>有効</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>はい/いいえ</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>所在地2</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr"/>
+      <c r="E82" s="7" t="inlineStr"/>
       <c r="F82" s="7" t="inlineStr"/>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>はい</t>
-        </is>
-      </c>
+      <c r="G82" s="7" t="inlineStr"/>
+      <c r="H82" s="7" t="inlineStr"/>
       <c r="I82" s="8" t="inlineStr"/>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>address2</t>
         </is>
       </c>
       <c r="K82" s="8" t="inlineStr"/>
@@ -6773,44 +7014,44 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>CtnGaiji</t>
+          <t>CtnIrbs</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CtnActive</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>アイテムID</t>
+          <t>有効</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>数値（標準）</t>
+          <t>はい/いいえ</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="F83" s="7" t="inlineStr">
-        <is>
           <t>○</t>
         </is>
       </c>
+      <c r="F83" s="7" t="inlineStr"/>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="H83" s="7" t="inlineStr"/>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
       <c r="I83" s="8" t="inlineStr"/>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K83" s="8" t="inlineStr"/>
@@ -6823,38 +7064,42 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>表示名</t>
+          <t>アイテムID</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>数値（標準）</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F84" s="7" t="inlineStr"/>
-      <c r="G84" s="7" t="inlineStr"/>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
       <c r="H84" s="7" t="inlineStr"/>
       <c r="I84" s="8" t="inlineStr"/>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>（組立値）</t>
-        </is>
-      </c>
-      <c r="K84" s="8" t="inlineStr">
-        <is>
-          <t>例「D-0003 髙→高」</t>
-        </is>
-      </c>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="K84" s="8" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -6864,17 +7109,17 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>CtnDoctor</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>医師</t>
+          <t>表示名</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>参照（CtnDoctors）</t>
+          <t>単一行</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -6883,21 +7128,17 @@
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="G85" s="7" t="inlineStr"/>
       <c r="H85" s="7" t="inlineStr"/>
       <c r="I85" s="8" t="inlineStr"/>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>doctorId</t>
+          <t>（組立値）</t>
         </is>
       </c>
       <c r="K85" s="8" t="inlineStr">
         <is>
-          <t>医師ごとの確認履歴</t>
+          <t>例「D-0003 髙→高」</t>
         </is>
       </c>
     </row>
@@ -6909,30 +7150,42 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>CtnNotification</t>
+          <t>CtnDoctor</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>検出発生届</t>
+          <t>医師</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>参照（CtnNotifications）</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr"/>
+          <t>参照（CtnDoctors）</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F86" s="7" t="inlineStr"/>
-      <c r="G86" s="7" t="inlineStr"/>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="H86" s="7" t="inlineStr"/>
       <c r="I86" s="8" t="inlineStr"/>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>notificationId</t>
-        </is>
-      </c>
-      <c r="K86" s="8" t="inlineStr"/>
+          <t>doctorId</t>
+        </is>
+      </c>
+      <c r="K86" s="8" t="inlineStr">
+        <is>
+          <t>医師ごとの確認履歴</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
@@ -6942,38 +7195,30 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>CtnTargetColumn</t>
+          <t>CtnNotification</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>対象列</t>
+          <t>検出発生届</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>参照（CtnNotifications）</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr"/>
       <c r="F87" s="7" t="inlineStr"/>
       <c r="G87" s="7" t="inlineStr"/>
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="8" t="inlineStr"/>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>targetColumn</t>
-        </is>
-      </c>
-      <c r="K87" s="8" t="inlineStr">
-        <is>
-          <t>例「CtnDoctors.CtnNameOriginal」</t>
-        </is>
-      </c>
+          <t>notificationId</t>
+        </is>
+      </c>
+      <c r="K87" s="8" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
@@ -6983,12 +7228,12 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>CtnOriginalChar</t>
+          <t>CtnTargetColumn</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>元字</t>
+          <t>対象列</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -7004,17 +7249,17 @@
       <c r="F88" s="7" t="inlineStr"/>
       <c r="G88" s="7" t="inlineStr"/>
       <c r="H88" s="7" t="inlineStr"/>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>1文字</t>
-        </is>
-      </c>
+      <c r="I88" s="8" t="inlineStr"/>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>originalChar</t>
-        </is>
-      </c>
-      <c r="K88" s="8" t="inlineStr"/>
+          <t>targetColumn</t>
+        </is>
+      </c>
+      <c r="K88" s="8" t="inlineStr">
+        <is>
+          <t>例「CtnDoctors.CtnNameOriginal」</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -7024,12 +7269,12 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>CtnCodePoint</t>
+          <t>CtnOriginalChar</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>コードポイント</t>
+          <t>元字</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -7047,101 +7292,101 @@
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr">
         <is>
+          <t>1文字</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>originalChar</t>
+        </is>
+      </c>
+      <c r="K89" s="8" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>CtnGaiji</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>CtnCodePoint</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>コードポイント</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>単一行</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr"/>
+      <c r="G90" s="7" t="inlineStr"/>
+      <c r="H90" s="7" t="inlineStr"/>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
           <t>U+XXXX</t>
         </is>
       </c>
-      <c r="J89" s="7" t="inlineStr">
+      <c r="J90" s="7" t="inlineStr">
         <is>
           <t>codePoint</t>
         </is>
       </c>
-      <c r="K89" s="8" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="12" t="inlineStr">
+      <c r="K90" s="8" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
         <is>
           <t>CtnGaiji</t>
         </is>
       </c>
-      <c r="B90" s="13" t="inlineStr">
+      <c r="B91" s="13" t="inlineStr">
         <is>
           <t>CtnReplacementChar</t>
         </is>
       </c>
-      <c r="C90" s="14" t="inlineStr">
+      <c r="C91" s="14" t="inlineStr">
         <is>
           <t>代替字</t>
         </is>
       </c>
-      <c r="D90" s="12" t="inlineStr">
+      <c r="D91" s="12" t="inlineStr">
         <is>
           <t>単一行</t>
         </is>
       </c>
-      <c r="E90" s="12" t="inlineStr">
+      <c r="E91" s="12" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F90" s="12" t="inlineStr"/>
-      <c r="G90" s="12" t="inlineStr"/>
-      <c r="H90" s="12" t="inlineStr"/>
-      <c r="I90" s="14" t="inlineStr">
+      <c r="F91" s="12" t="inlineStr"/>
+      <c r="G91" s="12" t="inlineStr"/>
+      <c r="H91" s="12" t="inlineStr"/>
+      <c r="I91" s="14" t="inlineStr">
         <is>
           <t>1文字</t>
         </is>
       </c>
-      <c r="J90" s="12" t="inlineStr">
+      <c r="J91" s="12" t="inlineStr">
         <is>
           <t>replacementChar</t>
         </is>
       </c>
-      <c r="K90" s="14" t="inlineStr">
+      <c r="K91" s="14" t="inlineStr">
         <is>
           <t>⚠要確認（縮退マップは本番で標準＋社内辞書に差し替え）</t>
         </is>
       </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>CtnGaiji</t>
-        </is>
-      </c>
-      <c r="B91" s="11" t="inlineStr">
-        <is>
-          <t>CtnGaijiType</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>判定区分</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr"/>
-      <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="7" t="inlineStr"/>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t>JIS外/機種依存/IVS/私用領域</t>
-        </is>
-      </c>
-      <c r="J91" s="7" t="inlineStr">
-        <is>
-          <t>gaijiType</t>
-        </is>
-      </c>
-      <c r="K91" s="8" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -7151,17 +7396,17 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>CtnConfirmedBy</t>
+          <t>CtnGaijiType</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>確認者</t>
+          <t>判定区分</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>数値</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -7174,19 +7419,15 @@
       <c r="H92" s="7" t="inlineStr"/>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>loginName</t>
+          <t>JIS外/機種依存/IVS/私用領域</t>
         </is>
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>confirmedBy</t>
-        </is>
-      </c>
-      <c r="K92" s="8" t="inlineStr">
-        <is>
-          <t>人間の確認を必須にする（自動置換のみで完結させない）</t>
-        </is>
-      </c>
+          <t>gaijiType</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
@@ -7196,12 +7437,12 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>CtnConfirmedOn</t>
+          <t>CtnConfirmedBy</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>確認日時</t>
+          <t>確認者</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -7219,57 +7460,57 @@
       <c r="H93" s="7" t="inlineStr"/>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>ISO8601</t>
+          <t>loginName</t>
         </is>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>confirmedOn</t>
-        </is>
-      </c>
-      <c r="K93" s="8" t="inlineStr"/>
+          <t>confirmedBy</t>
+        </is>
+      </c>
+      <c r="K93" s="8" t="inlineStr">
+        <is>
+          <t>人間の確認を必須にする（自動置換のみで完結させない）</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>CtnAudit</t>
+          <t>CtnGaiji</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CtnConfirmedOn</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>アイテムID</t>
+          <t>確認日時</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>数値（標準）</t>
+          <t>単一行</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>自動</t>
-        </is>
-      </c>
+      <c r="F94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr"/>
       <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="8" t="inlineStr"/>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>confirmedOn</t>
         </is>
       </c>
       <c r="K94" s="8" t="inlineStr"/>
@@ -7282,31 +7523,39 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>表示名</t>
+          <t>アイテムID</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>数値（標準）</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr"/>
-      <c r="G95" s="7" t="inlineStr"/>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
       <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr"/>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>（組立値）</t>
+          <t>id</t>
         </is>
       </c>
       <c r="K95" s="8" t="inlineStr"/>
@@ -7319,12 +7568,12 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>CtnAt</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>発生日時</t>
+          <t>表示名</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -7338,27 +7587,15 @@
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="G96" s="7" t="inlineStr"/>
       <c r="H96" s="7" t="inlineStr"/>
-      <c r="I96" s="8" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="I96" s="8" t="inlineStr"/>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>at</t>
-        </is>
-      </c>
-      <c r="K96" s="8" t="inlineStr">
-        <is>
-          <t>★インデックス必須（既定ビューの並べ替え＋期間フィルタ）</t>
-        </is>
-      </c>
+          <t>（組立値）</t>
+        </is>
+      </c>
+      <c r="K96" s="8" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
@@ -7368,12 +7605,12 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>CtnWho</t>
+          <t>CtnAt</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>操作者</t>
+          <t>発生日時</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -7395,17 +7632,17 @@
       <c r="H97" s="7" t="inlineStr"/>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>loginName</t>
+          <t>ISO8601</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>who</t>
+          <t>at</t>
         </is>
       </c>
       <c r="K97" s="8" t="inlineStr">
         <is>
-          <t>pageContext から取得</t>
+          <t>★インデックス必須（既定ビューの並べ替え＋期間フィルタ）</t>
         </is>
       </c>
     </row>
@@ -7417,17 +7654,17 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>CtnAction</t>
+          <t>CtnWho</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>操作者</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>選択肢</t>
+          <t>単一行</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
@@ -7444,15 +7681,19 @@
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>create / update / delete / restore / submit / approve / generate-xml</t>
+          <t>loginName</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>action</t>
-        </is>
-      </c>
-      <c r="K98" s="8" t="inlineStr"/>
+          <t>who</t>
+        </is>
+      </c>
+      <c r="K98" s="8" t="inlineStr">
+        <is>
+          <t>pageContext から取得</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -7462,17 +7703,17 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>CtnEntity</t>
+          <t>CtnAction</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>対象</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>選択肢</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
@@ -7481,19 +7722,23 @@
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
-      <c r="G99" s="7" t="inlineStr"/>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="H99" s="7" t="inlineStr"/>
-      <c r="I99" s="8" t="inlineStr"/>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>create / update / delete / restore / submit / approve / generate-xml</t>
+        </is>
+      </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>entity</t>
-        </is>
-      </c>
-      <c r="K99" s="8" t="inlineStr">
-        <is>
-          <t>リスト表示名</t>
-        </is>
-      </c>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="K99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
@@ -7503,12 +7748,12 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>CtnEntityRef</t>
+          <t>CtnEntity</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>対象識別子</t>
+          <t>対象</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -7522,19 +7767,19 @@
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="G100" s="7" t="inlineStr"/>
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="8" t="inlineStr"/>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>entityRef</t>
-        </is>
-      </c>
-      <c r="K100" s="8" t="inlineStr"/>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="K100" s="8" t="inlineStr">
+        <is>
+          <t>リスト表示名</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
@@ -7544,17 +7789,17 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>CtnSummary</t>
+          <t>CtnEntityRef</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>対象識別子</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>複数行</t>
+          <t>単一行</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -7563,66 +7808,58 @@
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
-      <c r="G101" s="7" t="inlineStr"/>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="H101" s="7" t="inlineStr"/>
       <c r="I101" s="8" t="inlineStr"/>
       <c r="J101" s="7" t="inlineStr">
         <is>
+          <t>entityRef</t>
+        </is>
+      </c>
+      <c r="K101" s="8" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>CtnAudit</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>CtnSummary</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>複数行</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr"/>
+      <c r="G102" s="7" t="inlineStr"/>
+      <c r="H102" s="7" t="inlineStr"/>
+      <c r="I102" s="8" t="inlineStr"/>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="K101" s="8" t="inlineStr">
+      <c r="K102" s="8" t="inlineStr">
         <is>
           <t>何を・どう変えたか</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="9" t="inlineStr">
-        <is>
-          <t>CtnSettings★</t>
-        </is>
-      </c>
-      <c r="B102" s="15" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C102" s="10" t="inlineStr">
-        <is>
-          <t>設定名</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>単一行</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G102" s="9" t="inlineStr"/>
-      <c r="H102" s="9" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="I102" s="10" t="inlineStr"/>
-      <c r="J102" s="9" t="inlineStr">
-        <is>
-          <t>（固定）</t>
-        </is>
-      </c>
-      <c r="K102" s="10" t="inlineStr">
-        <is>
-          <t>単一アイテム運用。アイテムを増やさない</t>
         </is>
       </c>
     </row>
@@ -7634,17 +7871,17 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>CtnOffset30</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>30日調査の期限オフセット</t>
+          <t>設定名</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>数値（整数）</t>
+          <t>単一行</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
@@ -7652,26 +7889,26 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F103" s="9" t="inlineStr"/>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="G103" s="9" t="inlineStr"/>
       <c r="H103" s="9" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I103" s="10" t="inlineStr">
-        <is>
-          <t>日数</t>
-        </is>
-      </c>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="I103" s="10" t="inlineStr"/>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>offset30</t>
+          <t>（固定）</t>
         </is>
       </c>
       <c r="K103" s="10" t="inlineStr">
         <is>
-          <t>治験開始予定日 − N日。★変更は提出期限の全再計算に波及する</t>
+          <t>単一アイテム運用。アイテムを増やさない</t>
         </is>
       </c>
     </row>
@@ -7683,12 +7920,12 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>CtnOffset14</t>
+          <t>CtnOffset30</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>通常の期限オフセット</t>
+          <t>30日調査の期限オフセット</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
@@ -7705,7 +7942,7 @@
       <c r="G104" s="9" t="inlineStr"/>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
@@ -7715,10 +7952,14 @@
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>offset14</t>
-        </is>
-      </c>
-      <c r="K104" s="10" t="inlineStr"/>
+          <t>offset30</t>
+        </is>
+      </c>
+      <c r="K104" s="10" t="inlineStr">
+        <is>
+          <t>治験開始予定日 − N日。★変更は提出期限の全再計算に波及する</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
@@ -7728,12 +7969,12 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>CtnWarnDays</t>
+          <t>CtnOffset14</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>期限接近アラート（黄）閾値</t>
+          <t>通常の期限オフセット</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
@@ -7760,7 +8001,7 @@
       </c>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>warnDays</t>
+          <t>offset14</t>
         </is>
       </c>
       <c r="K105" s="10" t="inlineStr"/>
@@ -7773,12 +8014,12 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>CtnHotDays</t>
+          <t>CtnWarnDays</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>期限接近アラート（赤）閾値</t>
+          <t>期限接近アラート（黄）閾値</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
@@ -7795,7 +8036,7 @@
       <c r="G106" s="9" t="inlineStr"/>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I106" s="10" t="inlineStr">
@@ -7805,7 +8046,7 @@
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>hotDays</t>
+          <t>warnDays</t>
         </is>
       </c>
       <c r="K106" s="10" t="inlineStr"/>
@@ -7818,12 +8059,12 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>CtnInquiryDays</t>
+          <t>CtnHotDays</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>PMDA照会リマインダ閾値</t>
+          <t>期限接近アラート（赤）閾値</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
@@ -7840,7 +8081,7 @@
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I107" s="10" t="inlineStr">
@@ -7850,7 +8091,7 @@
       </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>inquiryDays</t>
+          <t>hotDays</t>
         </is>
       </c>
       <c r="K107" s="10" t="inlineStr"/>
@@ -7863,12 +8104,12 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>CtnBatchMonths</t>
+          <t>CtnInquiryDays</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>定期報告バッチ</t>
+          <t>PMDA照会リマインダ閾値</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
@@ -7885,24 +8126,20 @@
       <c r="G108" s="9" t="inlineStr"/>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I108" s="10" t="inlineStr">
         <is>
-          <t>か月</t>
+          <t>日数</t>
         </is>
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>batchMonths</t>
-        </is>
-      </c>
-      <c r="K108" s="10" t="inlineStr">
-        <is>
-          <t>分担医師の異動のみが対象</t>
-        </is>
-      </c>
+          <t>inquiryDays</t>
+        </is>
+      </c>
+      <c r="K108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
@@ -7912,17 +8149,17 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>CtnOverdue</t>
+          <t>CtnBatchMonths</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>期限超過アラート</t>
+          <t>定期報告バッチ</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>はい/いいえ</t>
+          <t>数値（整数）</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
@@ -7934,16 +8171,24 @@
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>はい</t>
-        </is>
-      </c>
-      <c r="I109" s="10" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I109" s="10" t="inlineStr">
+        <is>
+          <t>か月</t>
+        </is>
+      </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="K109" s="10" t="inlineStr"/>
+          <t>batchMonths</t>
+        </is>
+      </c>
+      <c r="K109" s="10" t="inlineStr">
+        <is>
+          <t>分担医師の異動のみが対象</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
@@ -7953,12 +8198,12 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>CtnSubmitReminder</t>
+          <t>CtnOverdue</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>提出待ちリマインダ</t>
+          <t>期限超過アラート</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
@@ -7981,7 +8226,7 @@
       <c r="I110" s="10" t="inlineStr"/>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>submitReminder</t>
+          <t>overdue</t>
         </is>
       </c>
       <c r="K110" s="10" t="inlineStr"/>
@@ -7994,12 +8239,12 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>CtnInquiryReminder</t>
+          <t>CtnSubmitReminder</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>PMDA照会リマインダ</t>
+          <t>提出待ちリマインダ</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
@@ -8022,7 +8267,7 @@
       <c r="I111" s="10" t="inlineStr"/>
       <c r="J111" s="9" t="inlineStr">
         <is>
-          <t>inquiryReminder</t>
+          <t>submitReminder</t>
         </is>
       </c>
       <c r="K111" s="10" t="inlineStr"/>
@@ -8035,12 +8280,12 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>CtnBatchReminder</t>
+          <t>CtnInquiryReminder</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>定期報告 保留リマインダ</t>
+          <t>PMDA照会リマインダ</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
@@ -8063,7 +8308,7 @@
       <c r="I112" s="10" t="inlineStr"/>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>batchReminder</t>
+          <t>inquiryReminder</t>
         </is>
       </c>
       <c r="K112" s="10" t="inlineStr"/>
@@ -8071,44 +8316,40 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>CtnAppUsers★</t>
+          <t>CtnSettings★</t>
         </is>
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CtnBatchReminder</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>アイテムID</t>
+          <t>定期報告 保留リマインダ</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>数値（標準）</t>
+          <t>はい/いいえ</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="F113" s="9" t="inlineStr">
-        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G113" s="9" t="inlineStr">
-        <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="H113" s="9" t="inlineStr"/>
+      <c r="F113" s="9" t="inlineStr"/>
+      <c r="G113" s="9" t="inlineStr"/>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
       <c r="I113" s="10" t="inlineStr"/>
       <c r="J113" s="9" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>batchReminder</t>
         </is>
       </c>
       <c r="K113" s="10" t="inlineStr"/>
@@ -8121,31 +8362,39 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>表示名</t>
+          <t>アイテムID</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>単一行</t>
+          <t>数値（標準）</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F114" s="9" t="inlineStr"/>
-      <c r="G114" s="9" t="inlineStr"/>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
       <c r="H114" s="9" t="inlineStr"/>
       <c r="I114" s="10" t="inlineStr"/>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="K114" s="10" t="inlineStr"/>
@@ -8158,12 +8407,12 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>CtnLoginName</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>ログイン名</t>
+          <t>表示名</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
@@ -8176,32 +8425,16 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F115" s="9" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G115" s="9" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="F115" s="9" t="inlineStr"/>
+      <c r="G115" s="9" t="inlineStr"/>
       <c r="H115" s="9" t="inlineStr"/>
-      <c r="I115" s="10" t="inlineStr">
-        <is>
-          <t>UPN</t>
-        </is>
-      </c>
+      <c r="I115" s="10" t="inlineStr"/>
       <c r="J115" s="9" t="inlineStr">
         <is>
-          <t>（新規）</t>
-        </is>
-      </c>
-      <c r="K115" s="10" t="inlineStr">
-        <is>
-          <t>★pageContext.user.loginName と突合するキー</t>
-        </is>
-      </c>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="K115" s="10" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
@@ -8211,12 +8444,12 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>CtnInitials</t>
+          <t>CtnLoginName</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>イニシャル</t>
+          <t>ログイン名</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
@@ -8224,19 +8457,35 @@
           <t>単一行</t>
         </is>
       </c>
-      <c r="E116" s="9" t="inlineStr"/>
-      <c r="F116" s="9" t="inlineStr"/>
-      <c r="G116" s="9" t="inlineStr"/>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="H116" s="9" t="inlineStr"/>
-      <c r="I116" s="10" t="inlineStr"/>
+      <c r="I116" s="10" t="inlineStr">
+        <is>
+          <t>UPN</t>
+        </is>
+      </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>initials</t>
+          <t>（新規）</t>
         </is>
       </c>
       <c r="K116" s="10" t="inlineStr">
         <is>
-          <t>アバター表示用</t>
+          <t>★pageContext.user.loginName と突合するキー</t>
         </is>
       </c>
     </row>
@@ -8248,48 +8497,32 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>CtnRole</t>
+          <t>CtnInitials</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>ロール</t>
+          <t>イニシャル</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>選択肢</t>
-        </is>
-      </c>
-      <c r="E117" s="9" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>単一行</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr"/>
       <c r="F117" s="9" t="inlineStr"/>
-      <c r="G117" s="9" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H117" s="9" t="inlineStr">
-        <is>
-          <t>drafter</t>
-        </is>
-      </c>
-      <c r="I117" s="10" t="inlineStr">
-        <is>
-          <t>drafter / reviewer / approver / regulatory</t>
-        </is>
-      </c>
+      <c r="G117" s="9" t="inlineStr"/>
+      <c r="H117" s="9" t="inlineStr"/>
+      <c r="I117" s="10" t="inlineStr"/>
       <c r="J117" s="9" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>initials</t>
         </is>
       </c>
       <c r="K117" s="10" t="inlineStr">
         <is>
-          <t>★承認可否・設定変更可否の判定に使用</t>
+          <t>アバター表示用</t>
         </is>
       </c>
     </row>
@@ -8301,30 +8534,50 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>CtnDept</t>
+          <t>CtnRole</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>所属</t>
+          <t>ロール</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>単一行</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr"/>
+          <t>選択肢</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F118" s="9" t="inlineStr"/>
-      <c r="G118" s="9" t="inlineStr"/>
-      <c r="H118" s="9" t="inlineStr"/>
-      <c r="I118" s="10" t="inlineStr"/>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>drafter</t>
+        </is>
+      </c>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>drafter / reviewer / approver / regulatory</t>
+        </is>
+      </c>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>dept</t>
-        </is>
-      </c>
-      <c r="K118" s="10" t="inlineStr"/>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>★承認可否・設定変更可否の判定に使用</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
@@ -8334,39 +8587,27 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>CtnActive</t>
+          <t>CtnDept</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>有効</t>
+          <t>所属</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>はい/いいえ</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>単一行</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr"/>
       <c r="F119" s="9" t="inlineStr"/>
-      <c r="G119" s="9" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H119" s="9" t="inlineStr">
-        <is>
-          <t>はい</t>
-        </is>
-      </c>
+      <c r="G119" s="9" t="inlineStr"/>
+      <c r="H119" s="9" t="inlineStr"/>
       <c r="I119" s="10" t="inlineStr"/>
       <c r="J119" s="9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>dept</t>
         </is>
       </c>
       <c r="K119" s="10" t="inlineStr"/>
@@ -8374,22 +8615,22 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>CtnAttachmentFiles★</t>
+          <t>CtnAppUsers★</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>FileLeafRef</t>
+          <t>CtnActive</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>ファイル名</t>
+          <t>有効</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>標準（ファイル）</t>
+          <t>はい/いいえ</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
@@ -8398,23 +8639,23 @@
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>
-      <c r="G120" s="9" t="inlineStr"/>
-      <c r="H120" s="9" t="inlineStr"/>
-      <c r="I120" s="10" t="inlineStr">
-        <is>
-          <t>255バイト以内</t>
-        </is>
-      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="I120" s="10" t="inlineStr"/>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>docName</t>
-        </is>
-      </c>
-      <c r="K120" s="10" t="inlineStr">
-        <is>
-          <t>★checkByteLimit() の対象。将来フェーズ</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K120" s="10" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
@@ -8424,17 +8665,17 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>CtnNotification</t>
+          <t>FileLeafRef</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>届出</t>
+          <t>ファイル名</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>参照（CtnNotifications）</t>
+          <t>標準（ファイル）</t>
         </is>
       </c>
       <c r="E121" s="9" t="inlineStr">
@@ -8443,19 +8684,23 @@
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr"/>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="G121" s="9" t="inlineStr"/>
       <c r="H121" s="9" t="inlineStr"/>
-      <c r="I121" s="10" t="inlineStr"/>
+      <c r="I121" s="10" t="inlineStr">
+        <is>
+          <t>255バイト以内</t>
+        </is>
+      </c>
       <c r="J121" s="9" t="inlineStr">
         <is>
-          <t>（Payload側 id）</t>
-        </is>
-      </c>
-      <c r="K121" s="10" t="inlineStr"/>
+          <t>docName</t>
+        </is>
+      </c>
+      <c r="K121" s="10" t="inlineStr">
+        <is>
+          <t>★checkByteLimit() の対象。将来フェーズ</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
@@ -8465,17 +8710,17 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>CtnDocType</t>
+          <t>CtnNotification</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>資料種別</t>
+          <t>届出</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>数値</t>
+          <t>参照（CtnNotifications）</t>
         </is>
       </c>
       <c r="E122" s="9" t="inlineStr">
@@ -8490,14 +8735,10 @@
         </is>
       </c>
       <c r="H122" s="9" t="inlineStr"/>
-      <c r="I122" s="10" t="inlineStr">
-        <is>
-          <t>Protocol / IB / ICF ほか</t>
-        </is>
-      </c>
+      <c r="I122" s="10" t="inlineStr"/>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>docType</t>
+          <t>（Payload側 id）</t>
         </is>
       </c>
       <c r="K122" s="10" t="inlineStr"/>
@@ -8510,38 +8751,42 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>CtnHasBookmarks</t>
+          <t>CtnDocType</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>しおり付与</t>
+          <t>資料種別</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>はい/いいえ</t>
-        </is>
-      </c>
-      <c r="E123" s="9" t="inlineStr"/>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F123" s="9" t="inlineStr"/>
-      <c r="G123" s="9" t="inlineStr"/>
-      <c r="H123" s="9" t="inlineStr">
-        <is>
-          <t>いいえ</t>
-        </is>
-      </c>
-      <c r="I123" s="10" t="inlineStr"/>
+      <c r="G123" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="inlineStr"/>
+      <c r="I123" s="10" t="inlineStr">
+        <is>
+          <t>Protocol / IB / ICF ほか</t>
+        </is>
+      </c>
       <c r="J123" s="9" t="inlineStr">
         <is>
-          <t>hasBookmarks</t>
-        </is>
-      </c>
-      <c r="K123" s="10" t="inlineStr">
-        <is>
-          <t>PMDA提出要件のチェック</t>
-        </is>
-      </c>
+          <t>docType</t>
+        </is>
+      </c>
+      <c r="K123" s="10" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
@@ -8551,12 +8796,12 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>CtnHasText</t>
+          <t>CtnHasBookmarks</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>テキスト含有</t>
+          <t>しおり付与</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
@@ -8575,12 +8820,12 @@
       <c r="I124" s="10" t="inlineStr"/>
       <c r="J124" s="9" t="inlineStr">
         <is>
-          <t>hasText</t>
+          <t>hasBookmarks</t>
         </is>
       </c>
       <c r="K124" s="10" t="inlineStr">
         <is>
-          <t>スキャンPDF検出用</t>
+          <t>PMDA提出要件のチェック</t>
         </is>
       </c>
     </row>
@@ -8592,41 +8837,414 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>CtnAttachStatus</t>
+          <t>CtnHasText</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>添付ステータス</t>
+          <t>テキスト含有</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E125" s="9" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>はい/いいえ</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr"/>
       <c r="F125" s="9" t="inlineStr"/>
       <c r="G125" s="9" t="inlineStr"/>
-      <c r="H125" s="9" t="inlineStr"/>
-      <c r="I125" s="10" t="inlineStr">
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="I125" s="10" t="inlineStr"/>
+      <c r="J125" s="9" t="inlineStr">
+        <is>
+          <t>hasText</t>
+        </is>
+      </c>
+      <c r="K125" s="10" t="inlineStr">
+        <is>
+          <t>スキャンPDF検出用</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>CtnAttachmentFiles★</t>
+        </is>
+      </c>
+      <c r="B126" s="15" t="inlineStr">
+        <is>
+          <t>CtnAttachStatus</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>添付ステータス</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr"/>
+      <c r="G126" s="9" t="inlineStr"/>
+      <c r="H126" s="9" t="inlineStr"/>
+      <c r="I126" s="10" t="inlineStr">
         <is>
           <t>添付済 / 確認中 / 任意</t>
         </is>
       </c>
-      <c r="J125" s="9" t="inlineStr">
+      <c r="J126" s="9" t="inlineStr">
         <is>
           <t>attachStatus</t>
         </is>
       </c>
-      <c r="K125" s="10" t="inlineStr"/>
+      <c r="K126" s="10" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>CtnGeneratedOutputs★</t>
+        </is>
+      </c>
+      <c r="B127" s="15" t="inlineStr">
+        <is>
+          <t>FileLeafRef</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>ファイル名</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>標準（ファイル）</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr"/>
+      <c r="G127" s="9" t="inlineStr"/>
+      <c r="H127" s="9" t="inlineStr"/>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>255バイト以内</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="inlineStr">
+        <is>
+          <t>（組立値）</t>
+        </is>
+      </c>
+      <c r="K127" s="10" t="inlineStr">
+        <is>
+          <t>例「AMG410_届2変1_治験計画変更届_20260726.pdf」。★checkByteLimit() の対象</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>CtnGeneratedOutputs★</t>
+        </is>
+      </c>
+      <c r="B128" s="15" t="inlineStr">
+        <is>
+          <t>CtnNotification</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>届出</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>参照（CtnNotifications）</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr"/>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H128" s="9" t="inlineStr"/>
+      <c r="I128" s="10" t="inlineStr"/>
+      <c r="J128" s="9" t="inlineStr">
+        <is>
+          <t>（Notification id）</t>
+        </is>
+      </c>
+      <c r="K128" s="10" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>CtnGeneratedOutputs★</t>
+        </is>
+      </c>
+      <c r="B129" s="15" t="inlineStr">
+        <is>
+          <t>CtnOutputKind</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>生成物種別</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>選択肢</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr"/>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H129" s="9" t="inlineStr"/>
+      <c r="I129" s="10" t="inlineStr">
+        <is>
+          <t>pdf-review / pdf-submission / xml</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="inlineStr">
+        <is>
+          <t>（新規）</t>
+        </is>
+      </c>
+      <c r="K129" s="10" t="inlineStr">
+        <is>
+          <t>★pdf-review=社内レビュー用（現行・ラスタライズ）／pdf-submission=提出用（将来・テキスト選択可）</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>CtnGeneratedOutputs★</t>
+        </is>
+      </c>
+      <c r="B130" s="15" t="inlineStr">
+        <is>
+          <t>CtnGeneratedAt</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>生成日時</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>単一行</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr"/>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H130" s="9" t="inlineStr"/>
+      <c r="I130" s="10" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
+          <t>（新規）</t>
+        </is>
+      </c>
+      <c r="K130" s="10" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>CtnGeneratedOutputs★</t>
+        </is>
+      </c>
+      <c r="B131" s="15" t="inlineStr">
+        <is>
+          <t>CtnGeneratedBy</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>生成者</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>単一行</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr"/>
+      <c r="G131" s="9" t="inlineStr"/>
+      <c r="H131" s="9" t="inlineStr"/>
+      <c r="I131" s="10" t="inlineStr">
+        <is>
+          <t>loginName</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="inlineStr">
+        <is>
+          <t>（新規）</t>
+        </is>
+      </c>
+      <c r="K131" s="10" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>CtnGeneratedOutputs★</t>
+        </is>
+      </c>
+      <c r="B132" s="15" t="inlineStr">
+        <is>
+          <t>CtnPageCount</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>ページ数</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>数値（整数）</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr"/>
+      <c r="F132" s="9" t="inlineStr"/>
+      <c r="G132" s="9" t="inlineStr"/>
+      <c r="H132" s="9" t="inlineStr"/>
+      <c r="I132" s="10" t="inlineStr"/>
+      <c r="J132" s="9" t="inlineStr">
+        <is>
+          <t>（新規）</t>
+        </is>
+      </c>
+      <c r="K132" s="10" t="inlineStr">
+        <is>
+          <t>PDFのみ。output.ts の pageCount</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>CtnGeneratedOutputs★</t>
+        </is>
+      </c>
+      <c r="B133" s="15" t="inlineStr">
+        <is>
+          <t>CtnPackingLists</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>結合した添付数</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>数値（整数）</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr"/>
+      <c r="F133" s="9" t="inlineStr"/>
+      <c r="G133" s="9" t="inlineStr"/>
+      <c r="H133" s="9" t="inlineStr"/>
+      <c r="I133" s="10" t="inlineStr"/>
+      <c r="J133" s="9" t="inlineStr">
+        <is>
+          <t>（新規）</t>
+        </is>
+      </c>
+      <c r="K133" s="10" t="inlineStr">
+        <is>
+          <t>検査キット/パッキングリストの結合件数。output.ts の packingListsIncluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>CtnGeneratedOutputs★</t>
+        </is>
+      </c>
+      <c r="B134" s="15" t="inlineStr">
+        <is>
+          <t>CtnPayloadVersionAtGen</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>生成時ペイロード版</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>単一行</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr"/>
+      <c r="F134" s="9" t="inlineStr"/>
+      <c r="G134" s="9" t="inlineStr"/>
+      <c r="H134" s="9" t="inlineStr"/>
+      <c r="I134" s="10" t="inlineStr"/>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>（新規）</t>
+        </is>
+      </c>
+      <c r="K134" s="10" t="inlineStr">
+        <is>
+          <t>どの版の Payload から生成したかの追跡。再生成時の同一性確認に使う</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K125"/>
+  <autoFilter ref="A5:K134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17353,7 +17971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -18706,11 +19324,11 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>検査キット/パッキングリスト</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>100001207</v>
+        <v>100001208</v>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
@@ -18726,23 +19344,27 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>添付ステータス</t>
+          <t>資料種別</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>添付済</t>
+          <t>その他</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>100001300</v>
+        <v>100001207</v>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Payload $.attachments[].attachStatus（数値）</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr"/>
+          <t>Payload $.attachments[].docType（数値）</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>届出区分により必要セットが変化</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -18752,11 +19374,11 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>確認中</t>
+          <t>添付済</t>
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>100001301</v>
+        <v>100001300</v>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
@@ -18773,11 +19395,11 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>確認中</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>100001302</v>
+        <v>100001301</v>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
@@ -18789,27 +19411,23 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>IRB区分</t>
+          <t>添付ステータス</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>院内</t>
+          <t>任意</t>
         </is>
       </c>
       <c r="C64" s="7" t="n">
-        <v>100001400</v>
+        <v>100001302</v>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>CtnIrbs.CtnIrbType（数値）</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>TYPEIRBに対応</t>
-        </is>
-      </c>
+          <t>Payload $.attachments[].attachStatus（数値）</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -18819,11 +19437,11 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>外部</t>
+          <t>院内</t>
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>100001401</v>
+        <v>100001400</v>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
@@ -18839,25 +19457,25 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>外字判定区分</t>
+          <t>IRB区分</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>JIS水準外</t>
+          <t>外部</t>
         </is>
       </c>
       <c r="C66" s="7" t="n">
-        <v>100001500</v>
+        <v>100001401</v>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>CtnGaiji.CtnGaijiType（数値）</t>
+          <t>CtnIrbs.CtnIrbType（数値）</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>外字検出プラグインの判定結果</t>
+          <t>TYPEIRBに対応</t>
         </is>
       </c>
     </row>
@@ -18869,11 +19487,11 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>機種依存</t>
+          <t>JIS水準外</t>
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>100001501</v>
+        <v>100001500</v>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
@@ -18894,11 +19512,11 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>IVS</t>
+          <t>機種依存</t>
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>100001502</v>
+        <v>100001501</v>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
@@ -18919,25 +19537,50 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
+          <t>IVS</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>100001502</v>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>CtnGaiji.CtnGaijiType（数値）</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>外字検出プラグインの判定結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>外字判定区分</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
           <t>PUA</t>
         </is>
       </c>
-      <c r="C69" s="7" t="n">
+      <c r="C70" s="7" t="n">
         <v>100001503</v>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>CtnGaiji.CtnGaijiType（数値）</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>外字検出プラグインの判定結果</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:E69"/>
+  <autoFilter ref="A5:E70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18948,7 +19591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -19915,8 +20558,118 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>届書PDF生成（社内レビュー用）</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>（構想に無し）</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>治験届</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>提出パッケージ出力の操作時</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>クライアント。PrintableNotification を html2canvas でラスタライズ → pdf-lib でページ化</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>output.ts generateSubmissionPackage()</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Cat 5</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>★現行は社内レビュー用。ラスタライズのためテキスト選択不可。PMDA 提出用へ格上げする際は Word テンプレート＋SharePoint のファイル変換によるサーバー側生成へ切り替える</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>提出パッケージ結合</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>（構想に無し）</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>治験届＋添付</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>提出パッケージ出力の操作時</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>クライアント。資料種別「検査キット/パッキングリスト」(100001208) の実PDFを届書PDFへ結合</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>output.ts generateSubmissionPackage()</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Cat 5</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>★デモはサンプルPDFを生成。本番で実ファイルを結合する段階で CtnAttachmentFiles が必須になる</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:K21"/>
+  <autoFilter ref="A5:K23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19927,7 +20680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20503,215 +21256,257 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>マスタ管理</t>
+          <t>治験届 詳細</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>医療機関・医師・IRB・届出者・現場担当のCRUD</t>
+          <t>提出パッケージ出力（届書PDF＋CTN XML）</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>create/update/setXxxActive()</t>
+          <t>（新規）saveGeneratedOutput()</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>各マスタリスト</t>
+          <t>CtnNotifications 一式, CtnAttachmentFiles（実ファイル結合時）</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>各マスタリスト, CtnAudit（＋医師は CtnGaiji）</t>
+          <t>CtnGeneratedOutputs（アップロード）, CtnNotifications（CtnPdfGeneratedAt / CtnXmlGeneratedAt）, CtnAudit</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>POST / MERGE</t>
+          <t>POST /Files/add + MERGE</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>detectGaiji()（医師のみ）</t>
+          <t>output.ts generateSubmissionPackage() / xml.ts</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>★物理削除しない。無効化は CtnActive=いいえ</t>
+          <t>★現行の届書PDFは社内レビュー用（ラスタライズ）。生成物は上書きせず版を積む。PMDA 提出用へ格上げする際はサーバー側生成（Word テンプレート＋ファイル変換）へ切り替える</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>外字確認ダイアログ</t>
+          <t>マスタ管理</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>代替字の確認・記録</t>
+          <t>医療機関・医師・IRB・届出者・現場担当のCRUD</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>addGaijiRecord()</t>
+          <t>create/update/setXxxActive()</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>CtnDoctors</t>
+          <t>各マスタリスト</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>CtnGaiji（追記）, CtnDoctors（届出用表記）</t>
+          <t>各マスタリスト, CtnAudit（＋医師は CtnGaiji）</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>POST /items</t>
+          <t>POST / MERGE</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>normalizeGaiji()</t>
+          <t>detectGaiji()（医師のみ）</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>人間の確認結果を記録してから届出用表記を確定する</t>
+          <t>★物理削除しない。無効化は CtnActive=いいえ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>データ取り込み</t>
+          <t>外字確認ダイアログ</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>既存XMLの読込→ドラフト化</t>
+          <t>代替字の確認・記録</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>createNotification() + updateNotification()</t>
+          <t>addGaijiRecord()</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>CtnCompounds</t>
+          <t>CtnDoctors</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>CtnCompounds（無ければ作成）, CtnNotifications, CtnAudit</t>
+          <t>CtnGaiji（追記）, CtnDoctors（届出用表記）</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>POST / MERGE</t>
+          <t>POST /items</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>XMLパース</t>
+          <t>normalizeGaiji()</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>取り込み結果は必ず下書き。提出前に人間が補完する</t>
+          <t>人間の確認結果を記録してから届出用表記を確定する</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>ロジカルチェック設定</t>
+          <t>データ取り込み</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>閾値・有効/無効の変更</t>
+          <t>既存XMLの読込→ドラフト化</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>（新規）updateSettings()</t>
+          <t>createNotification() + updateNotification()</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>CtnSettings</t>
+          <t>CtnCompounds</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>CtnSettings（更新）, CtnAudit</t>
+          <t>CtnCompounds（無ければ作成）, CtnNotifications, CtnAudit</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>MERGE</t>
+          <t>POST / MERGE</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>XMLパース</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>★全利用者共通の設定。更新は薬事担当ロールに限定し、変更は監査へ記録する</t>
+          <t>取り込み結果は必ず下書き。提出前に人間が補完する</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
+          <t>ロジカルチェック設定</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>閾値・有効/無効の変更</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>（新規）updateSettings()</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>CtnSettings</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>CtnSettings（更新）, CtnAudit</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>★全利用者共通の設定。更新は薬事担当ロールに限定し、変更は監査へ記録する</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
           <t>監査ログ</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>一覧・絞り込み</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>—（読み取りのみ）</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>CtnAudit</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>GET（$filter=CtnAt ge ...&amp;$top=...）</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>★5,000件しきい値の主要対策対象。CtnAt にインデックス必須</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H22"/>
+  <autoFilter ref="A5:H23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20722,7 +21517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -21056,27 +21851,71 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>クライアント側PDF生成の限界</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>SPFx はブラウザ内実行のみ</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>html2canvas によるラスタライズPDFはテキストを含まない。★ctn-schema.json が cr_hastext（テキスト含有チェック）を PDF 品質要件として持つことと矛盾する</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>社内レビュー用途では許容。PMDA 提出用へ格上げする際は Word テンプレート＋SharePoint の「ファイルの変換」（標準コネクタ・追加費用なし）によるサーバー側生成へ切り替える</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>バンドルサイズ</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>SPFx はバンドルが大きいと初期表示が遅い</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>pdf-lib + html2canvas の追加で自己完結デモが約450KB → 約1,081KB に増加</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>現規模では許容。日本語フォント埋め込み（Noto Sans JP で数MB増）は行わない。サーバー側生成へ移せばクライアントから両ライブラリを外せる</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>添付ファイル</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>リストアイテムの添付は検索・メタデータ管理に弱い</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Protocol / IB / ICF の版管理・しおり有無チェックに不足</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>ドキュメントライブラリ（CtnAttachmentFiles）＋メタデータ列で管理（将来フェーズ）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:D19"/>
+  <autoFilter ref="A5:D21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>